--- a/concept/src/test/java/selenium/training/assignment/ten/TestCredentials.xlsx
+++ b/concept/src/test/java/selenium/training/assignment/ten/TestCredentials.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>User ID</t>
   </si>
@@ -43,15 +43,6 @@
   </si>
   <si>
     <t>Test@123</t>
-  </si>
-  <si>
-    <t>ExpectedOutcome</t>
-  </si>
-  <si>
-    <t>pass</t>
-  </si>
-  <si>
-    <t>fail</t>
   </si>
 </sst>
 </file>
@@ -117,11 +108,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -395,7 +385,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -403,56 +393,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
